--- a/output/rev05a/topic_table.xlsx
+++ b/output/rev05a/topic_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ABI\__MATA KULIAH PASCA\TESIS\output\rev05a\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pythonAppGado\__thes is\karya-ilmiah-master\output\rev05a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBFD329-55D2-4ABD-8CE2-EFA5D7C70DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FA6A14-E6F8-4463-966A-CADB824B8FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,12 +127,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -141,7 +138,15 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Disitribusi </a:t>
+              <a:t>Dokumen</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> vs Topik</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> </a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -159,12 +164,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -196,13 +198,39 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:cat>
             <c:numRef>
@@ -540,36 +568,69 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Topik</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                  <a:alpha val="32000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:majorGridlines>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
+              <a:schemeClr val="tx2">
                 <a:lumMod val="15000"/>
                 <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
-            <a:tailEnd type="none" w="med" len="lg"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -580,10 +641,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -611,10 +669,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
-                  <a:alpha val="32000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -622,21 +679,63 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Jumlah Dokumen</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-            <a:tailEnd type="none" w="med" len="lg"/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -647,10 +746,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -673,7 +769,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="t"/>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -689,10 +785,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -705,7 +798,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -713,6 +805,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -720,7 +813,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="tx2">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -788,39 +881,32 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="237">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="281">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
-        <a:tailEnd type="none" w="med" len="lg"/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -830,7 +916,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -838,7 +924,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -853,10 +939,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
@@ -865,9 +948,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -890,84 +972,69 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
+      <a:ln w="31750" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:miter lim="800000"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700">
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="lt2"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -983,15 +1050,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1005,13 +1069,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
@@ -1029,16 +1093,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -1047,16 +1112,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:errorBar>
@@ -1065,23 +1130,33 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
-            <a:alpha val="32000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1093,15 +1168,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
-            <a:alpha val="32000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -1112,13 +1186,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
         </a:solidFill>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -1127,12 +1205,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
@@ -1145,27 +1223,24 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -1173,18 +1248,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
-        <a:tailEnd type="none" w="med" len="lg"/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1194,16 +1268,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -1212,12 +1287,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1226,10 +1298,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="rnd"/>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
     </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
@@ -1237,10 +1314,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
@@ -1249,7 +1323,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -1258,8 +1332,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -1270,23 +1344,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-        <a:tailEnd type="none" w="med" len="lg"/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1294,7 +1353,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -1342,9 +1401,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1382,9 +1441,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1417,9 +1476,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1452,9 +1528,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1629,9 +1722,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>-1</v>
       </c>
@@ -1647,7 +1740,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1655,7 +1748,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1663,7 +1756,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1671,7 +1764,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1679,7 +1772,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1687,7 +1780,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1695,7 +1788,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1703,7 +1796,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1711,7 +1804,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1719,7 +1812,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1727,7 +1820,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1735,7 +1828,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1743,7 +1836,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1751,7 +1844,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1759,7 +1852,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1767,7 +1860,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1775,7 +1868,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1783,7 +1876,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1791,7 +1884,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1799,7 +1892,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1807,7 +1900,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1815,7 +1908,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -1823,7 +1916,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1831,7 +1924,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -1839,7 +1932,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1847,7 +1940,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -1855,7 +1948,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -1863,7 +1956,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -1871,7 +1964,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -1879,7 +1972,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -1887,7 +1980,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -1895,7 +1988,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -1903,7 +1996,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -1911,7 +2004,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -1919,7 +2012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -1927,7 +2020,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -1935,7 +2028,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -1943,7 +2036,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -1951,7 +2044,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -1959,7 +2052,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -1967,7 +2060,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -1975,7 +2068,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -1983,7 +2076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -1991,7 +2084,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -1999,7 +2092,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -2007,7 +2100,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -2015,7 +2108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -2023,7 +2116,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
